--- a/assets/liptx-antioxidants.xlsx
+++ b/assets/liptx-antioxidants.xlsx
@@ -504,7 +504,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
@@ -519,7 +519,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ranked strongest → lightest by antioxidant potency in skin science.  Formula UC1001.4  ·  Appose · The Reflect Co.</t>
+          <t>Ranked strongest → lightest by antioxidant potency.  What each does for the lips.  Formula UC1001.4  ·  Appose · The Reflect Co.</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>What it does</t>
+          <t>What it does for the lips</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Neutralizes UV free radicals; supports elasticity.</t>
+          <t>Defends lips from UV oxidative aging; supports elasticity.</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Scavenges reactive oxygen from UV stress.</t>
+          <t>Second layer of UV defense for delicate lip skin.</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Brightens tone; builds collagen; oil-soluble C.</t>
+          <t>Brightens lip tone; builds collagen around the mouth.</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Quenches singlet oxygen; blocks UV photodamage.</t>
+          <t>Blocks UV damage that causes lip fine lines.</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Fat-soluble Vitamin C; protects lipid layers.</t>
+          <t>Delivers Vitamin C into the lip's lipid barrier.</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Free-radical scavenger; provitamin A.</t>
+          <t>Protects lips from sun stress; subtle rosy tint.</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Calms inflammation; supports healing.</t>
+          <t>Calms chapping and irritation; supports lip healing.</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Protects membranes; reduces water loss.</t>
+          <t>Softens lips; locks in moisture, prevents drying.</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Drives cell turnover and renewal.</t>
+          <t>Renews lip skin cells; keeps lips smooth.</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Powers SOD enzyme; supports collagen.</t>
+          <t>Supports collagen for lip volume and fewer lines.</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Enzyme cofactor; strengthens skin barrier.</t>
+          <t>Strengthens the lip barrier; speeds chapping recovery.</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Peng J, et al. "Fucoxanthin, a Marine Carotenoid Present in Brown Seaweeds and Diatoms: Metabolism and Bioactivities Relevant to Human Health." Marine Drugs. 2011;9(10):1806-1828. https://www.mdpi.com/1660-3397/9/10/1806</t>
+          <t>Peng J, et al. "Fucoxanthin, a Marine Carotenoid Present in Brown Seaweeds and Diatoms." Marine Drugs. 2011;9(10):1806-1828. https://www.mdpi.com/1660-3397/9/10/1806</t>
         </is>
       </c>
     </row>
